--- a/docs/구글시트_양식.xlsx
+++ b/docs/구글시트_양식.xlsx
@@ -173,7 +173,7 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>프로그래밍, 원화, 기획, BGM, 그래픽, AI, 대회, 대학, 채용, 기타</t>
+        <t>프로그래밍, 원화, 기획, BGM, 그래픽, AI, 대회, 채용, 기타</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -218,7 +218,7 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>프로그래밍, 원화, 기획, BGM, 그래픽, AI, 대회, 대학, 채용, 기타</t>
+        <t>프로그래밍, 원화, 기획, BGM, 그래픽, AI, 대회, 채용, 기타</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -263,12 +263,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>구분 / 장르 / 제외</t>
+        <t>구분 / 장르 / 제외 / 대학 / 대학과목</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>구분·장르 이름. 제외는 비워 둠</t>
+        <t>구분·장르 이름. 제외·대학·대학과목은 비워 둠</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -650,46 +650,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 종류는 구분 / 장르 / 제외 중 하나. '제외'는 제목에 들어 있으면 수집하지 않는 단어입니다.</t>
+          <t xml:space="preserve">  - 종류는 구분 / 장르 / 제외 / 대학 / 대학과목 중 하나. '제외'는 제목에 들어 있으면 수집하지 않는 단어입니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>■ 수집사이트 탭: 사이트별로 수집을 켜고(O) 끕니다(X).</t>
+          <t xml:space="preserve">  - '대학'은 웹툰·게임·애니 관련 학과가 있는 대학 이름(줄임말), '대학과목'은 그 대학 공모전으로 인정할 과목 단어입니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    제목에 대학 이름이 있고 과목 단어가 함께 나오면 '대학' 탭에 들어갑니다. ('○○대학교'라고 적힌 제목은 목록에 없어도 인식)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>날짜는 2026-11-30 형식으로 적습니다.</t>
+          <t>■ 수집사이트 탭: 사이트별로 수집을 켜고(O) 끕니다(X).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>수정 내용은 다음 자동 실행(08시·18시)에 반영됩니다. 바로 반영하려면 GitHub Actions에서 'Run workflow'를 누르세요.</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>반영하지 못한 줄은 사이트의 /review/ 페이지 위쪽에 표시됩니다.</t>
+          <t>날짜는 2026-11-30 형식으로 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>수정 내용은 다음 자동 실행(08시·18시)에 반영됩니다. 바로 반영하려면 GitHub Actions에서 'Run workflow'를 누르세요.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>반영하지 못한 줄은 사이트의 /review/ 페이지 위쪽에 표시됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>이 시트는 '웹에 게시(CSV)'로 공개되므로, 공개되어도 괜찮은 내용만 적어 주세요.</t>
         </is>
@@ -706,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -908,12 +922,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-bbe503</t>
+          <t>2026-5dc34a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026 레진성인공모전</t>
+          <t>2027년 현대경제신문 신춘문예 공모</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -931,12 +945,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-bf2c91</t>
+          <t>2026-bbe503</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>금단의 사랑 —넘쳐버린 욕망, 멈출 수 없는 탐닉</t>
+          <t>2026 레진성인공모전</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -947,19 +961,19 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>자동: 제목 확인</t>
+          <t>자동: 분류 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-e88a3a</t>
+          <t>2026-bf2c91</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>제39회 무등일보 신춘문예 공모</t>
+          <t>금단의 사랑 —넘쳐버린 욕망, 멈출 수 없는 탐닉</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -970,19 +984,19 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>자동: 분류 확인 필요</t>
+          <t>자동: 제목 확인</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-23cd88</t>
+          <t>2026-827efe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>실상문학 신인문학상 작품 모집</t>
+          <t>세계일보 2027 신춘문예 공모</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -1000,12 +1014,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-7ebdf8</t>
+          <t>2026-4cd7f1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>제5회 책읽는곰 어린이책 공모전</t>
+          <t>2027 국제신문 신춘문예 공모</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -1023,12 +1037,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-e5fb1e</t>
+          <t>2026-e88a3a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>소소한설 공모전</t>
+          <t>제39회 무등일보 신춘문예 공모</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1046,12 +1060,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-0cf819</t>
+          <t>2026-d33a23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[레드립] 19세 단행본 투고 접수(2026년 상시)</t>
+          <t>2027 광남일보 한국문학대상</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1062,19 +1076,19 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>자동: URL 없음</t>
+          <t>자동: 분류 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-0f89f3</t>
+          <t>2026-23cd88</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>제4회 현대문학x미래엔 청소년문학상 공모전</t>
+          <t>실상문학 신인문학상 작품 모집</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1092,12 +1106,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-311162</t>
+          <t>2026-7ebdf8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2027 제3회 소원문학상</t>
+          <t>제5회 책읽는곰 어린이책 공모전</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1115,12 +1129,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2027-80b8c1</t>
+          <t>2026-e5fb1e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>제17회 천강문학상 작품 공모</t>
+          <t>소소한설 공모전</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1138,12 +1152,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-7ac627</t>
+          <t>2026-0cf819</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>제2회 블루카이트 창작 글쓰기 대회 (참가비 있음)</t>
+          <t>[레드립] 19세 단행본 투고 접수(2026년 상시)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1154,19 +1168,19 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>자동: 분류 확인 필요</t>
+          <t>자동: URL 없음</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2027-72cdce</t>
+          <t>2026-0f89f3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2027 창비 청소년 문학상 공모</t>
+          <t>제4회 현대문학x미래엔 청소년문학상 공모전</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1184,12 +1198,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-4cefe8</t>
+          <t>2026-311162</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>제1회 우리학교 청소년 문학상 공모</t>
+          <t>2027 제3회 소원문학상</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1204,16 +1218,108 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2027-80b8c1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>제17회 천강문학상 작품 공모</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>자동: 분류 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-7ac627</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>제2회 블루카이트 창작 글쓰기 대회 (참가비 있음)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>자동: 분류 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2027-72cdce</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2027 창비 청소년 문학상 공모</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>자동: 분류 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-4cefe8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>제1회 우리학교 청소년 문학상 공모</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>자동: 분류 확인 필요</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="숨기려면 O" type="list">
       <formula1>"O"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로 (예: 웹툰, 게임)" type="list">
-      <formula1>"웹툰,웹소설,게임"</formula1>
+      <formula1>"웹툰,웹소설,게임,대학"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로" type="list">
-      <formula1>"프로그래밍,원화,기획,BGM,그래픽,AI,대회,대학,채용,기타"</formula1>
+      <formula1>"프로그래밍,원화,기획,BGM,그래픽,AI,대회,채용,기타"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로" type="list">
       <formula1>"초등학생,중학생,고등학생,대학생,대학원생,일반(누구나)"</formula1>
@@ -1306,10 +1412,10 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로" type="list">
-      <formula1>"웹툰,웹소설,게임"</formula1>
+      <formula1>"웹툰,웹소설,게임,대학"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로" type="list">
-      <formula1>"프로그래밍,원화,기획,BGM,그래픽,AI,대회,대학,채용,기타"</formula1>
+      <formula1>"프로그래밍,원화,기획,BGM,그래픽,AI,대회,채용,기타"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로" type="list">
       <formula1>"초등학생,중학생,고등학생,대학생,대학원생,일반(누구나)"</formula1>
@@ -1329,10 +1435,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="110" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1367,7 +1473,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>웹툰, 만화, 인스타툰, 컷툰, 콘티, 코믹스, 노블코믹스, 그림책, webtoon, comic, manga</t>
+          <t>웹툰, 만화, 인스타툰, 컷툰, 콘티, 코믹스, 노블코믹스, 그림책, 애니메이션, 칸만화, 카툰, webtoon, comic, manga, animation</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1638,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>대학</t>
+          <t>채용</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>대학교 주최, 실기대전, 입학특전, 입시</t>
+          <t>인턴, 인턴십, 채용, 서포터즈, 기자단</t>
         </is>
       </c>
     </row>
@@ -1549,49 +1655,58 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>채용</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>인턴, 인턴십, 채용, 서포터즈, 기자단</t>
+          <t>비평, 보드게임</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>장르</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>비평, 보드게임</t>
+          <t>수상자 발표, 수상작 발표, 결과 발표, 결과발표, 인증 이벤트, 댓글 이벤트, 체험단, 서평단, 참여단, 평가단, 사진 공모, 사진공모, 슬로건, 네이밍, 명칭 공모, 브랜드 네이밍, 논문, 모금광고, ttrpg, tabletop, bundle, lewd, nsfw, 18+, zine</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>대학</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>수상자 발표, 수상작 발표, 결과 발표, 결과발표, 인증 이벤트, 댓글 이벤트, 체험단, 서평단, 참여단, 평가단, 사진 공모, 사진공모, 슬로건, 네이밍, 명칭 공모, 브랜드 네이밍, 논문, 모금광고, ttrpg, tabletop, bundle, lewd, nsfw, 18+, zine</t>
+          <t>청강문화산업대, 청강대, 한국영상대, 동원대, 상명대, 서강대, 구미대, 수성대, 정화예술대, 정화예대, 연성대, 재능대, 목포대, 서원대, 동명대, 동서대, 대진대, 순천향대, 건국대, 세종대, 공주대, 목원대, 홍익대, 중부대, 전주대, 호서대, 경일대, 영산대, 우송대, 배재대, 인덕대, 계원예술대, 계원예대, 서울예술대, 서울예대, 동아방송예술대, 동아방송예대, 한국예술종합학교, 한예종, 한국공학대, 동의대, 부천대, 대덕대, 경민대, 백석예술대, 백석예대, 한서대, 청주대, 극동대, 부산경상대, 인제대, 조선대, 남서울대, 한세대</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>대학과목</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>웹툰, 만화, 칸만화, 카툰, 상황표현, 애니, 게임, 캐릭터, 일러스트, 웹소설, 스토리, 콘텐츠, 이모티콘</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="구분 / 장르 / 제외" type="list">
-      <formula1>"구분,장르,제외"</formula1>
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="구분 / 장르 / 제외 / 대학 / 대학과목" type="list">
+      <formula1>"구분,장르,제외,대학,대학과목"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1605,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1667,7 +1782,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itchio</t>
+          <t>mgood</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1677,22 +1792,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>itch.io — 해외 게임잼 (참가자 200명 이상)</t>
+          <t>엠굿(월간 미대입시) — 대학 주최 고등학생 웹툰·게임·애니 실기대회·공모전</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>itchio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>itch.io — 해외 게임잼 (참가자 200명 이상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>thinkcontest</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>씽굿 — 보류 (자동 수집 불가)</t>
         </is>

--- a/docs/구글시트_양식.xlsx
+++ b/docs/구글시트_양식.xlsx
@@ -168,30 +168,35 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>웹툰 / 웹소설 / 게임. 여러 개는 쉼표</t>
+        <t>경쟁사 관련 '승인 대기' 공모전: 승인(발행) / 거절(계속 숨김)</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
+        <t>웹툰 / 웹소설 / 게임 / 대학. 여러 개는 쉼표</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
         <t>프로그래밍, 원화, 기획, BGM, 그래픽, AI, 대회, 채용, 기타</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>초등학생, 중학생, 고등학생, 대학생, 대학원생, 일반(누구나)</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>예) 2026-11-30</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>사이트에 보일 제목을 바꿀 때만</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>운영자 메모. 사이트에는 반영되지 않음</t>
       </text>
@@ -263,12 +268,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>구분 / 장르 / 제외 / 대학 / 대학과목</t>
+        <t>구분 / 장르 / 제외 / 대학 / 대학과목 / 경쟁사</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>구분·장르 이름. 제외·대학·대학과목은 비워 둠</t>
+        <t>구분·장르 이름. 나머지는 비워 둠</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -589,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -650,7 +655,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 종류는 구분 / 장르 / 제외 / 대학 / 대학과목 중 하나. '제외'는 제목에 들어 있으면 수집하지 않는 단어입니다.</t>
+          <t xml:space="preserve">  - 종류는 구분 / 장르 / 제외 / 대학 / 대학과목 / 경쟁사 중 하나. '제외'는 제목에 들어 있으면 수집하지 않는 단어입니다.</t>
         </is>
       </c>
     </row>
@@ -671,39 +676,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>■ 수집사이트 탭: 사이트별로 수집을 켜고(O) 끕니다(X).</t>
+          <t xml:space="preserve">  - '경쟁사'에 적은 이름이 제목·주최·본문에 나오는 공모전은 사이트에 바로 올라가지 않고 '승인 대기'가 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>■ 승인 대기 처리: 관리자 페이지의 '승인 대기' 목록에서 ID를 복사 → 수정 탭에 붙여넣고 승인 칸에 '승인'(발행) 또는 '거절'(계속 숨김).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>날짜는 2026-11-30 형식으로 적습니다.</t>
+          <t>■ 수집사이트 탭: 사이트별로 수집을 켜고(O) 끕니다(X).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>수정 내용은 다음 자동 실행(08시·18시)에 반영됩니다. 바로 반영하려면 GitHub Actions에서 'Run workflow'를 누르세요.</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>반영하지 못한 줄은 사이트의 /review/ 페이지 위쪽에 표시됩니다.</t>
+          <t>날짜는 2026-11-30 형식으로 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>수정 내용은 다음 자동 실행(08시·18시)에 반영됩니다. 바로 반영하려면 GitHub Actions에서 'Run workflow'를 누르세요.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
+        <is>
+          <t>반영하지 못한 줄은 관리자 페이지 위쪽에 표시됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>이 시트는 '웹에 게시(CSV)'로 공개되므로, 공개되어도 괜찮은 내용만 적어 주세요.</t>
         </is>
@@ -720,18 +739,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -752,30 +772,35 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>승인</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>장르</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>대상</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>마감일</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>제목수정</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -798,7 +823,8 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -821,7 +847,8 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -844,7 +871,8 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>자동: 제목 확인</t>
         </is>
@@ -867,7 +895,8 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -890,7 +919,8 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -913,7 +943,8 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -936,7 +967,8 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -959,7 +991,8 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -982,7 +1015,8 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>자동: 제목 확인</t>
         </is>
@@ -1005,7 +1039,8 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1028,7 +1063,8 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1051,7 +1087,8 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1074,7 +1111,8 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1097,7 +1135,8 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1120,7 +1159,8 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1143,7 +1183,8 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1166,7 +1207,8 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>자동: URL 없음</t>
         </is>
@@ -1189,7 +1231,8 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1212,7 +1255,8 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1235,7 +1279,8 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1258,7 +1303,8 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1281,7 +1327,8 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
@@ -1304,24 +1351,28 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>자동: 분류 확인 필요</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="숨기려면 O" type="list">
       <formula1>"O"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로 (예: 웹툰, 게임)" type="list">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="승인: 사이트에 발행 / 거절: 계속 숨김" type="list">
+      <formula1>"승인,거절"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로 (예: 웹툰, 게임)" type="list">
       <formula1>"웹툰,웹소설,게임,대학"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로" type="list">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로" type="list">
       <formula1>"프로그래밍,원화,기획,BGM,그래픽,AI,대회,채용,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로" type="list">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="여러 개는 쉼표로" type="list">
       <formula1>"초등학생,중학생,고등학생,대학생,대학원생,일반(누구나)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1435,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1703,10 +1754,19 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>경쟁사</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="구분 / 장르 / 제외 / 대학 / 대학과목" type="list">
-      <formula1>"구분,장르,제외,대학,대학과목"</formula1>
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="입력 안내" prompt="구분 / 장르 / 제외 / 대학 / 대학과목 / 경쟁사" type="list">
+      <formula1>"구분,장르,제외,대학,대학과목,경쟁사"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
